--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2348">
   <si>
     <t>en</t>
   </si>
@@ -6607,445 +6607,448 @@
     <t>ねじれたワンダーランド</t>
   </si>
   <si>
+    <t>ULTRAKILL</t>
+  </si>
+  <si>
+    <t>ウルトラキル</t>
+  </si>
+  <si>
+    <t>Umineko - When They Cry</t>
+  </si>
+  <si>
+    <t>うみねこ - 彼らが泣くとき</t>
+  </si>
+  <si>
+    <t>Undertale</t>
+  </si>
+  <si>
+    <t>アンダーテール</t>
+  </si>
+  <si>
+    <t>Undertale AU</t>
+  </si>
+  <si>
+    <t>アンダーテールAU</t>
+  </si>
+  <si>
+    <t>Undertale Yellow</t>
+  </si>
+  <si>
+    <t>アンダーテイル イエロー</t>
+  </si>
+  <si>
+    <t>Universal Symbol</t>
+  </si>
+  <si>
+    <t>ユニバーサル・シンボル</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>上へ</t>
+  </si>
+  <si>
+    <t>Urban Wildlife</t>
+  </si>
+  <si>
+    <t>都会の野生動物</t>
+  </si>
+  <si>
+    <t>V for Vendetta</t>
+  </si>
+  <si>
+    <t>Vフォー・ヴェンデッタ</t>
+  </si>
+  <si>
+    <t>Valentines</t>
+  </si>
+  <si>
+    <t>バレンタイン</t>
+  </si>
+  <si>
+    <t>Valorant</t>
+  </si>
+  <si>
+    <t>バロラント</t>
+  </si>
+  <si>
+    <t>Vanilla (removed)</t>
+  </si>
+  <si>
+    <t>バニラ（除去）</t>
+  </si>
+  <si>
+    <t>Vanilla Block</t>
+  </si>
+  <si>
+    <t>バニラ・ブロック</t>
+  </si>
+  <si>
+    <t>Vanilla Food</t>
+  </si>
+  <si>
+    <t>バニラ・フード</t>
+  </si>
+  <si>
+    <t>Vanilla Helmet</t>
+  </si>
+  <si>
+    <t>バニラ・ヘルメット</t>
+  </si>
+  <si>
+    <t>Vanilla Item</t>
+  </si>
+  <si>
+    <t>バニラアイテム</t>
+  </si>
+  <si>
+    <t>Vanilla Mob</t>
+  </si>
+  <si>
+    <t>バニラ・モブ</t>
+  </si>
+  <si>
+    <t>Vault Hunters</t>
+  </si>
+  <si>
+    <t>ヴォールト・ハンターズ</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
+  </si>
+  <si>
+    <t>野菜</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>車両</t>
+  </si>
+  <si>
+    <t>Vikings</t>
+  </si>
+  <si>
+    <t>バイキングス</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>村人</t>
+  </si>
+  <si>
+    <t>Villager (Desert)</t>
+  </si>
+  <si>
+    <t>村人（砂漠）</t>
+  </si>
+  <si>
+    <t>Villager (Jungle)</t>
+  </si>
+  <si>
+    <t>村人（ジャングル）</t>
+  </si>
+  <si>
+    <t>Villager (Plains)</t>
+  </si>
+  <si>
+    <t>村人（平原）</t>
+  </si>
+  <si>
+    <t>Villager (Savanna)</t>
+  </si>
+  <si>
+    <t>村人（サバンナ）</t>
+  </si>
+  <si>
+    <t>Villager (Snowy Tundra)</t>
+  </si>
+  <si>
+    <t>村人（雪のツンドラ）</t>
+  </si>
+  <si>
+    <t>Villager (Swamp)</t>
+  </si>
+  <si>
+    <t>村人（沼地）</t>
+  </si>
+  <si>
+    <t>Villager (Taiga)</t>
+  </si>
+  <si>
+    <t>村人（タイガ）</t>
+  </si>
+  <si>
+    <t>Virtual Youtuber</t>
+  </si>
+  <si>
+    <t>バーチャルYoutuber</t>
+  </si>
+  <si>
+    <t>Vocaloid</t>
+  </si>
+  <si>
+    <t>ボーカロイド</t>
+  </si>
+  <si>
+    <t>Voltron</t>
+  </si>
+  <si>
+    <t>ボルトロン</t>
+  </si>
+  <si>
+    <t>Wakfu</t>
+  </si>
+  <si>
+    <t>和風</t>
+  </si>
+  <si>
+    <t>Walking Dead</t>
+  </si>
+  <si>
+    <t>ウォーキング・デッド</t>
+  </si>
+  <si>
+    <t>Wall-E</t>
+  </si>
+  <si>
+    <t>ウォール-E</t>
+  </si>
+  <si>
+    <t>Wallace and Gromit</t>
+  </si>
+  <si>
+    <t>ウォレスとグルミット</t>
+  </si>
+  <si>
+    <t>War of the Worlds</t>
+  </si>
+  <si>
+    <t>ウォー・オブ・ザ・ワールド</t>
+  </si>
+  <si>
+    <t>Warcraft</t>
+  </si>
+  <si>
+    <t>ウォークラフト</t>
+  </si>
+  <si>
+    <t>Warframe</t>
+  </si>
+  <si>
+    <t>ウォーフレーム</t>
+  </si>
+  <si>
+    <t>Warhammer</t>
+  </si>
+  <si>
+    <t>ウォーハンマー</t>
+  </si>
+  <si>
+    <t>Warrior Cats</t>
+  </si>
+  <si>
+    <t>ウォリアー・キャッツ</t>
+  </si>
+  <si>
+    <t>We Bear Bears</t>
+  </si>
+  <si>
+    <t>ウィー・ベア・ベアーズ</t>
+  </si>
+  <si>
+    <t>We Happy Few</t>
+  </si>
+  <si>
+    <t>ウィ・ハッピー・フュー</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>天気</t>
+  </si>
+  <si>
+    <t>Welcome Home</t>
+  </si>
+  <si>
+    <t>ウェルカムホーム</t>
+  </si>
+  <si>
+    <t>Who is this?</t>
+  </si>
+  <si>
+    <t>これは誰ですか？</t>
+  </si>
+  <si>
+    <t>Wild Update</t>
+  </si>
+  <si>
+    <t>ワイルド・アップデート</t>
+  </si>
+  <si>
+    <t>Wings of Fire</t>
+  </si>
+  <si>
+    <t>炎の翼</t>
+  </si>
+  <si>
+    <t>Winnie the Pooh</t>
+  </si>
+  <si>
+    <t>くまのプーさん</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>冬</t>
+  </si>
+  <si>
+    <t>Witcher</t>
+  </si>
+  <si>
+    <t>ウィッチャー</t>
+  </si>
+  <si>
+    <t>Wonderful Wonder World</t>
+  </si>
+  <si>
+    <t>ワンダフルワンダーワールド</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>木材</t>
+  </si>
+  <si>
+    <t>Wool</t>
+  </si>
+  <si>
+    <t>ウール</t>
+  </si>
+  <si>
+    <t>Work Safety Helmet</t>
+  </si>
+  <si>
+    <t>作業用安全ヘルメット</t>
+  </si>
+  <si>
+    <t>Wreck It Ralph</t>
+  </si>
+  <si>
+    <t>レック・イット・ラルフ</t>
+  </si>
+  <si>
+    <t>Wybel</t>
+  </si>
+  <si>
+    <t>ワイベル</t>
+  </si>
+  <si>
+    <t>Wynncraft</t>
+  </si>
+  <si>
+    <t>ウィンクラフト</t>
+  </si>
+  <si>
+    <t>X-Men</t>
+  </si>
+  <si>
+    <t>X-メン</t>
+  </si>
+  <si>
+    <t>Xenoblade Chronicles</t>
+  </si>
+  <si>
+    <t>ゼノブレイドクロニクル</t>
+  </si>
+  <si>
+    <t>Yandere Simulator</t>
+  </si>
+  <si>
+    <t>ヤンデレ・シミュレーター</t>
+  </si>
+  <si>
+    <t>Yellow Submarine</t>
+  </si>
+  <si>
+    <t>イエロー・サブマリン</t>
+  </si>
+  <si>
+    <t>Yokai</t>
+  </si>
+  <si>
+    <t>妖怪</t>
+  </si>
+  <si>
+    <t>Yooka Laylee</t>
+  </si>
+  <si>
+    <t>ユカ・レイリー</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>ヤング</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>Yu-Gi-Oh</t>
+  </si>
+  <si>
+    <t>遊戯王</t>
+  </si>
+  <si>
+    <t>Yume Nikki</t>
+  </si>
+  <si>
+    <t>夢日記</t>
+  </si>
+  <si>
+    <t>Zero no Tsukaima</t>
+  </si>
+  <si>
+    <t>ゼロの使い魔</t>
+  </si>
+  <si>
+    <t>Zero Wing</t>
+  </si>
+  <si>
+    <t>ゼロ・ウィング</t>
+  </si>
+  <si>
+    <t>Zodiac Sign</t>
+  </si>
+  <si>
+    <t>星座</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>ゾンビ</t>
+  </si>
+  <si>
+    <t>Zombie (Vanilla)</t>
+  </si>
+  <si>
+    <t>ゾンビ（バニラ）</t>
+  </si>
+  <si>
+    <t>Zootopia</t>
+  </si>
+  <si>
+    <t>ズートピア</t>
+  </si>
+  <si>
     <t>Ultrakill</t>
-  </si>
-  <si>
-    <t>ウルトラキル</t>
-  </si>
-  <si>
-    <t>Umineko - When They Cry</t>
-  </si>
-  <si>
-    <t>うみねこ - 彼らが泣くとき</t>
-  </si>
-  <si>
-    <t>Undertale</t>
-  </si>
-  <si>
-    <t>アンダーテール</t>
-  </si>
-  <si>
-    <t>Undertale AU</t>
-  </si>
-  <si>
-    <t>アンダーテールAU</t>
-  </si>
-  <si>
-    <t>Undertale Yellow</t>
-  </si>
-  <si>
-    <t>アンダーテイル イエロー</t>
-  </si>
-  <si>
-    <t>Universal Symbol</t>
-  </si>
-  <si>
-    <t>ユニバーサル・シンボル</t>
-  </si>
-  <si>
-    <t>Up</t>
-  </si>
-  <si>
-    <t>上へ</t>
-  </si>
-  <si>
-    <t>Urban Wildlife</t>
-  </si>
-  <si>
-    <t>都会の野生動物</t>
-  </si>
-  <si>
-    <t>V for Vendetta</t>
-  </si>
-  <si>
-    <t>Vフォー・ヴェンデッタ</t>
-  </si>
-  <si>
-    <t>Valentines</t>
-  </si>
-  <si>
-    <t>バレンタイン</t>
-  </si>
-  <si>
-    <t>Valorant</t>
-  </si>
-  <si>
-    <t>バロラント</t>
-  </si>
-  <si>
-    <t>Vanilla (removed)</t>
-  </si>
-  <si>
-    <t>バニラ（除去）</t>
-  </si>
-  <si>
-    <t>Vanilla Block</t>
-  </si>
-  <si>
-    <t>バニラ・ブロック</t>
-  </si>
-  <si>
-    <t>Vanilla Food</t>
-  </si>
-  <si>
-    <t>バニラ・フード</t>
-  </si>
-  <si>
-    <t>Vanilla Helmet</t>
-  </si>
-  <si>
-    <t>バニラ・ヘルメット</t>
-  </si>
-  <si>
-    <t>Vanilla Item</t>
-  </si>
-  <si>
-    <t>バニラアイテム</t>
-  </si>
-  <si>
-    <t>Vanilla Mob</t>
-  </si>
-  <si>
-    <t>バニラ・モブ</t>
-  </si>
-  <si>
-    <t>Vault Hunters</t>
-  </si>
-  <si>
-    <t>ヴォールト・ハンターズ</t>
-  </si>
-  <si>
-    <t>Vegetable</t>
-  </si>
-  <si>
-    <t>野菜</t>
-  </si>
-  <si>
-    <t>Vehicle</t>
-  </si>
-  <si>
-    <t>車両</t>
-  </si>
-  <si>
-    <t>Vikings</t>
-  </si>
-  <si>
-    <t>バイキングス</t>
-  </si>
-  <si>
-    <t>Villager</t>
-  </si>
-  <si>
-    <t>村人</t>
-  </si>
-  <si>
-    <t>Villager (Desert)</t>
-  </si>
-  <si>
-    <t>村人（砂漠）</t>
-  </si>
-  <si>
-    <t>Villager (Jungle)</t>
-  </si>
-  <si>
-    <t>村人（ジャングル）</t>
-  </si>
-  <si>
-    <t>Villager (Plains)</t>
-  </si>
-  <si>
-    <t>村人（平原）</t>
-  </si>
-  <si>
-    <t>Villager (Savanna)</t>
-  </si>
-  <si>
-    <t>村人（サバンナ）</t>
-  </si>
-  <si>
-    <t>Villager (Snowy Tundra)</t>
-  </si>
-  <si>
-    <t>村人（雪のツンドラ）</t>
-  </si>
-  <si>
-    <t>Villager (Swamp)</t>
-  </si>
-  <si>
-    <t>村人（沼地）</t>
-  </si>
-  <si>
-    <t>Villager (Taiga)</t>
-  </si>
-  <si>
-    <t>村人（タイガ）</t>
-  </si>
-  <si>
-    <t>Virtual Youtuber</t>
-  </si>
-  <si>
-    <t>バーチャルYoutuber</t>
-  </si>
-  <si>
-    <t>Vocaloid</t>
-  </si>
-  <si>
-    <t>ボーカロイド</t>
-  </si>
-  <si>
-    <t>Voltron</t>
-  </si>
-  <si>
-    <t>ボルトロン</t>
-  </si>
-  <si>
-    <t>Wakfu</t>
-  </si>
-  <si>
-    <t>和風</t>
-  </si>
-  <si>
-    <t>Walking Dead</t>
-  </si>
-  <si>
-    <t>ウォーキング・デッド</t>
-  </si>
-  <si>
-    <t>Wall-E</t>
-  </si>
-  <si>
-    <t>ウォール-E</t>
-  </si>
-  <si>
-    <t>Wallace and Gromit</t>
-  </si>
-  <si>
-    <t>ウォレスとグルミット</t>
-  </si>
-  <si>
-    <t>War of the Worlds</t>
-  </si>
-  <si>
-    <t>ウォー・オブ・ザ・ワールド</t>
-  </si>
-  <si>
-    <t>Warcraft</t>
-  </si>
-  <si>
-    <t>ウォークラフト</t>
-  </si>
-  <si>
-    <t>Warframe</t>
-  </si>
-  <si>
-    <t>ウォーフレーム</t>
-  </si>
-  <si>
-    <t>Warhammer</t>
-  </si>
-  <si>
-    <t>ウォーハンマー</t>
-  </si>
-  <si>
-    <t>Warrior Cats</t>
-  </si>
-  <si>
-    <t>ウォリアー・キャッツ</t>
-  </si>
-  <si>
-    <t>We Bear Bears</t>
-  </si>
-  <si>
-    <t>ウィー・ベア・ベアーズ</t>
-  </si>
-  <si>
-    <t>We Happy Few</t>
-  </si>
-  <si>
-    <t>ウィ・ハッピー・フュー</t>
-  </si>
-  <si>
-    <t>Weather</t>
-  </si>
-  <si>
-    <t>天気</t>
-  </si>
-  <si>
-    <t>Welcome Home</t>
-  </si>
-  <si>
-    <t>ウェルカムホーム</t>
-  </si>
-  <si>
-    <t>Who is this?</t>
-  </si>
-  <si>
-    <t>これは誰ですか？</t>
-  </si>
-  <si>
-    <t>Wild Update</t>
-  </si>
-  <si>
-    <t>ワイルド・アップデート</t>
-  </si>
-  <si>
-    <t>Wings of Fire</t>
-  </si>
-  <si>
-    <t>炎の翼</t>
-  </si>
-  <si>
-    <t>Winnie the Pooh</t>
-  </si>
-  <si>
-    <t>くまのプーさん</t>
-  </si>
-  <si>
-    <t>Winter</t>
-  </si>
-  <si>
-    <t>冬</t>
-  </si>
-  <si>
-    <t>Witcher</t>
-  </si>
-  <si>
-    <t>ウィッチャー</t>
-  </si>
-  <si>
-    <t>Wonderful Wonder World</t>
-  </si>
-  <si>
-    <t>ワンダフルワンダーワールド</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>木材</t>
-  </si>
-  <si>
-    <t>Wool</t>
-  </si>
-  <si>
-    <t>ウール</t>
-  </si>
-  <si>
-    <t>Work Safety Helmet</t>
-  </si>
-  <si>
-    <t>作業用安全ヘルメット</t>
-  </si>
-  <si>
-    <t>Wreck It Ralph</t>
-  </si>
-  <si>
-    <t>レック・イット・ラルフ</t>
-  </si>
-  <si>
-    <t>Wybel</t>
-  </si>
-  <si>
-    <t>ワイベル</t>
-  </si>
-  <si>
-    <t>Wynncraft</t>
-  </si>
-  <si>
-    <t>ウィンクラフト</t>
-  </si>
-  <si>
-    <t>X-Men</t>
-  </si>
-  <si>
-    <t>X-メン</t>
-  </si>
-  <si>
-    <t>Xenoblade Chronicles</t>
-  </si>
-  <si>
-    <t>ゼノブレイドクロニクル</t>
-  </si>
-  <si>
-    <t>Yandere Simulator</t>
-  </si>
-  <si>
-    <t>ヤンデレ・シミュレーター</t>
-  </si>
-  <si>
-    <t>Yellow Submarine</t>
-  </si>
-  <si>
-    <t>イエロー・サブマリン</t>
-  </si>
-  <si>
-    <t>Yokai</t>
-  </si>
-  <si>
-    <t>妖怪</t>
-  </si>
-  <si>
-    <t>Yooka Laylee</t>
-  </si>
-  <si>
-    <t>ユカ・レイリー</t>
-  </si>
-  <si>
-    <t>Young</t>
-  </si>
-  <si>
-    <t>ヤング</t>
-  </si>
-  <si>
-    <t>Youtube</t>
-  </si>
-  <si>
-    <t>Yu-Gi-Oh</t>
-  </si>
-  <si>
-    <t>遊戯王</t>
-  </si>
-  <si>
-    <t>Yume Nikki</t>
-  </si>
-  <si>
-    <t>夢日記</t>
-  </si>
-  <si>
-    <t>Zero no Tsukaima</t>
-  </si>
-  <si>
-    <t>ゼロの使い魔</t>
-  </si>
-  <si>
-    <t>Zero Wing</t>
-  </si>
-  <si>
-    <t>ゼロ・ウィング</t>
-  </si>
-  <si>
-    <t>Zodiac Sign</t>
-  </si>
-  <si>
-    <t>星座</t>
-  </si>
-  <si>
-    <t>Zombie</t>
-  </si>
-  <si>
-    <t>ゾンビ</t>
-  </si>
-  <si>
-    <t>Zombie (Vanilla)</t>
-  </si>
-  <si>
-    <t>ゾンビ（バニラ）</t>
-  </si>
-  <si>
-    <t>Zootopia</t>
-  </si>
-  <si>
-    <t>ズートピア</t>
   </si>
   <si>
     <t>Hypixel (Mutations) Tag</t>
@@ -7404,7 +7407,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1177"/>
+  <dimension ref="A1:B1178"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -16816,19 +16819,27 @@
         <v>2343</v>
       </c>
       <c r="B1176" t="s">
-        <v>2344</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
+        <v>2344</v>
+      </c>
+      <c r="B1177" t="s">
         <v>2345</v>
       </c>
-      <c r="B1177" t="s">
+    </row>
+    <row r="1178" spans="1:2">
+      <c r="A1178" t="s">
         <v>2346</v>
       </c>
+      <c r="B1178" t="s">
+        <v>2347</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1177"/>
+  <autoFilter ref="A1:B1178"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2350">
   <si>
     <t>en</t>
   </si>
@@ -4787,6 +4787,12 @@
   </si>
   <si>
     <t>オープンソースオブジェクト</t>
+  </si>
+  <si>
+    <t>Opus Magnum</t>
+  </si>
+  <si>
+    <t>オーパス・マグナム</t>
   </si>
   <si>
     <t>Orb</t>
@@ -7407,7 +7413,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1178"/>
+  <dimension ref="A1:B1179"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14443,12 +14449,12 @@
         <v>1752</v>
       </c>
       <c r="B879" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B880" t="s">
         <v>1754</v>
@@ -14739,12 +14745,12 @@
         <v>1825</v>
       </c>
       <c r="B916" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B917" t="s">
         <v>1827</v>
@@ -16747,12 +16753,12 @@
         <v>2326</v>
       </c>
       <c r="B1167" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="B1168" t="s">
         <v>2328</v>
@@ -16819,15 +16825,15 @@
         <v>2343</v>
       </c>
       <c r="B1176" t="s">
-        <v>2197</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="B1177" t="s">
-        <v>2345</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
@@ -16838,8 +16844,16 @@
         <v>2347</v>
       </c>
     </row>
+    <row r="1179" spans="1:2">
+      <c r="A1179" t="s">
+        <v>2348</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>2349</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1178"/>
+  <autoFilter ref="A1:B1179"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2352">
   <si>
     <t>en</t>
   </si>
@@ -989,6 +989,12 @@
   </si>
   <si>
     <t>聖杯</t>
+  </si>
+  <si>
+    <t>Chaos Cubed</t>
+  </si>
+  <si>
+    <t>カオス・キューブ</t>
   </si>
   <si>
     <t>Charlie and the Chocolate Factory</t>
@@ -7413,7 +7419,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1179"/>
+  <dimension ref="A1:B1180"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -9257,12 +9263,12 @@
         <v>458</v>
       </c>
       <c r="B230" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B231" t="s">
         <v>460</v>
@@ -9537,15 +9543,15 @@
         <v>527</v>
       </c>
       <c r="B265" t="s">
-        <v>494</v>
+        <v>528</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B266" t="s">
-        <v>529</v>
+        <v>496</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -10057,12 +10063,12 @@
         <v>656</v>
       </c>
       <c r="B330" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B331" t="s">
         <v>658</v>
@@ -11265,12 +11271,12 @@
         <v>957</v>
       </c>
       <c r="B481" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B482" t="s">
         <v>959</v>
@@ -14457,12 +14463,12 @@
         <v>1754</v>
       </c>
       <c r="B880" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B881" t="s">
         <v>1756</v>
@@ -14753,12 +14759,12 @@
         <v>1827</v>
       </c>
       <c r="B917" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B918" t="s">
         <v>1829</v>
@@ -16761,12 +16767,12 @@
         <v>2328</v>
       </c>
       <c r="B1168" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="B1169" t="s">
         <v>2330</v>
@@ -16833,15 +16839,15 @@
         <v>2345</v>
       </c>
       <c r="B1177" t="s">
-        <v>2199</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="B1178" t="s">
-        <v>2347</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
@@ -16852,8 +16858,16 @@
         <v>2349</v>
       </c>
     </row>
+    <row r="1180" spans="1:2">
+      <c r="A1180" t="s">
+        <v>2350</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>2351</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1179"/>
+  <autoFilter ref="A1:B1180"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2354">
   <si>
     <t>en</t>
   </si>
@@ -5183,6 +5183,12 @@
   </si>
   <si>
     <t>ポップ・チーム・エピック</t>
+  </si>
+  <si>
+    <t>Popee the Performer</t>
+  </si>
+  <si>
+    <t>ポピー・ザ・パフォーマー</t>
   </si>
   <si>
     <t>POPGOES</t>
@@ -7419,7 +7425,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1180"/>
+  <dimension ref="A1:B1181"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14471,12 +14477,12 @@
         <v>1756</v>
       </c>
       <c r="B881" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B882" t="s">
         <v>1758</v>
@@ -14767,12 +14773,12 @@
         <v>1829</v>
       </c>
       <c r="B918" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B919" t="s">
         <v>1831</v>
@@ -16775,12 +16781,12 @@
         <v>2330</v>
       </c>
       <c r="B1169" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="B1170" t="s">
         <v>2332</v>
@@ -16847,15 +16853,15 @@
         <v>2347</v>
       </c>
       <c r="B1178" t="s">
-        <v>2201</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="B1179" t="s">
-        <v>2349</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
@@ -16866,8 +16872,16 @@
         <v>2351</v>
       </c>
     </row>
+    <row r="1181" spans="1:2">
+      <c r="A1181" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>2353</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1180"/>
+  <autoFilter ref="A1:B1181"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2356">
   <si>
     <t>en</t>
   </si>
@@ -6467,6 +6467,12 @@
   </si>
   <si>
     <t>ティンカーズ・コンストラクト</t>
+  </si>
+  <si>
+    <t>Tiny Takeover</t>
+  </si>
+  <si>
+    <t>タイニー・テイクオーバー</t>
   </si>
   <si>
     <t>Titanfall</t>
@@ -7425,7 +7431,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1181"/>
+  <dimension ref="A1:B1182"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -16789,12 +16795,12 @@
         <v>2332</v>
       </c>
       <c r="B1170" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="B1171" t="s">
         <v>2334</v>
@@ -16861,15 +16867,15 @@
         <v>2349</v>
       </c>
       <c r="B1179" t="s">
-        <v>2203</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="B1180" t="s">
-        <v>2351</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
@@ -16880,8 +16886,16 @@
         <v>2353</v>
       </c>
     </row>
+    <row r="1182" spans="1:2">
+      <c r="A1182" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>2355</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1181"/>
+  <autoFilter ref="A1:B1182"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2364">
   <si>
     <t>en</t>
   </si>
@@ -3481,6 +3481,12 @@
     <t>ハイピクセル</t>
   </si>
   <si>
+    <t>Hypixel (Abiphone)</t>
+  </si>
+  <si>
+    <t>ハイピクセル（アビフォン）</t>
+  </si>
+  <si>
     <t>Hypixel (Attribute Shard)</t>
   </si>
   <si>
@@ -3505,6 +3511,12 @@
     <t>ハイピクセル（ギア）</t>
   </si>
   <si>
+    <t>Hypixel (Gemstone)</t>
+  </si>
+  <si>
+    <t>ハイピクセル（宝石）</t>
+  </si>
+  <si>
     <t>Hypixel (Minion)</t>
   </si>
   <si>
@@ -3523,6 +3535,12 @@
     <t>ハイピクセル（NPC）</t>
   </si>
   <si>
+    <t>Hypixel (Pet Items)</t>
+  </si>
+  <si>
+    <t>ハイピクセル（ペット用品）</t>
+  </si>
+  <si>
     <t>Hypixel (Pets)</t>
   </si>
   <si>
@@ -3533,6 +3551,12 @@
   </si>
   <si>
     <t>ハイピクセル（リフォージ・ストーン）</t>
+  </si>
+  <si>
+    <t>Hypixel (Runes)</t>
+  </si>
+  <si>
+    <t>ハイピクセル（ルーン文字）</t>
   </si>
   <si>
     <t>Hypixel (Sacks)</t>
@@ -7431,7 +7455,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1182"/>
+  <dimension ref="A1:B1186"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14491,36 +14515,36 @@
         <v>1758</v>
       </c>
       <c r="B882" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B883" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B884" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B885" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B886" t="s">
         <v>1766</v>
@@ -14787,36 +14811,36 @@
         <v>1831</v>
       </c>
       <c r="B919" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B920" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B921" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B922" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B923" t="s">
         <v>1839</v>
@@ -16803,36 +16827,36 @@
         <v>2334</v>
       </c>
       <c r="B1171" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="B1172" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="B1173" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="B1174" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="B1175" t="s">
         <v>2342</v>
@@ -16875,27 +16899,59 @@
         <v>2351</v>
       </c>
       <c r="B1180" t="s">
-        <v>2205</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="B1181" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="B1182" t="s">
-        <v>2355</v>
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:2">
+      <c r="A1183" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:2">
+      <c r="A1184" t="s">
+        <v>2359</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:2">
+      <c r="A1185" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:2">
+      <c r="A1186" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>2363</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1182"/>
+  <autoFilter ref="A1:B1186"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2366">
   <si>
     <t>en</t>
   </si>
@@ -5291,6 +5291,12 @@
   </si>
   <si>
     <t>レイトン教授</t>
+  </si>
+  <si>
+    <t>Project Zomboid</t>
+  </si>
+  <si>
+    <t>プロジェクト・ゾンボイド</t>
   </si>
   <si>
     <t>Pumpkin</t>
@@ -7455,7 +7461,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1186"/>
+  <dimension ref="A1:B1187"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14547,12 +14553,12 @@
         <v>1766</v>
       </c>
       <c r="B886" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B887" t="s">
         <v>1768</v>
@@ -14843,12 +14849,12 @@
         <v>1839</v>
       </c>
       <c r="B923" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B924" t="s">
         <v>1841</v>
@@ -16859,12 +16865,12 @@
         <v>2342</v>
       </c>
       <c r="B1175" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="B1176" t="s">
         <v>2344</v>
@@ -16931,15 +16937,15 @@
         <v>2359</v>
       </c>
       <c r="B1184" t="s">
-        <v>2213</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="B1185" t="s">
-        <v>2361</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
@@ -16950,8 +16956,16 @@
         <v>2363</v>
       </c>
     </row>
+    <row r="1187" spans="1:2">
+      <c r="A1187" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>2365</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1186"/>
+  <autoFilter ref="A1:B1187"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2368">
   <si>
     <t>en</t>
   </si>
@@ -425,6 +425,12 @@
   </si>
   <si>
     <t>バカとテスト</t>
+  </si>
+  <si>
+    <t>Bakugan</t>
+  </si>
+  <si>
+    <t>爆丸</t>
   </si>
   <si>
     <t>Baldi's Basics</t>
@@ -7461,7 +7467,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1187"/>
+  <dimension ref="A1:B1188"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -9313,12 +9319,12 @@
         <v>460</v>
       </c>
       <c r="B231" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B232" t="s">
         <v>462</v>
@@ -9593,15 +9599,15 @@
         <v>529</v>
       </c>
       <c r="B266" t="s">
-        <v>496</v>
+        <v>530</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B267" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -10113,12 +10119,12 @@
         <v>658</v>
       </c>
       <c r="B331" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B332" t="s">
         <v>660</v>
@@ -11321,12 +11327,12 @@
         <v>959</v>
       </c>
       <c r="B482" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B483" t="s">
         <v>961</v>
@@ -14561,12 +14567,12 @@
         <v>1768</v>
       </c>
       <c r="B887" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B888" t="s">
         <v>1770</v>
@@ -14857,12 +14863,12 @@
         <v>1841</v>
       </c>
       <c r="B924" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B925" t="s">
         <v>1843</v>
@@ -16873,12 +16879,12 @@
         <v>2344</v>
       </c>
       <c r="B1176" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="B1177" t="s">
         <v>2346</v>
@@ -16945,15 +16951,15 @@
         <v>2361</v>
       </c>
       <c r="B1185" t="s">
-        <v>2215</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="B1186" t="s">
-        <v>2363</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
@@ -16964,8 +16970,16 @@
         <v>2365</v>
       </c>
     </row>
+    <row r="1188" spans="1:2">
+      <c r="A1188" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>2367</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1187"/>
+  <autoFilter ref="A1:B1188"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2370">
   <si>
     <t>en</t>
   </si>
@@ -5687,6 +5687,12 @@
   </si>
   <si>
     <t>モルドールの影</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>サメ</t>
   </si>
   <si>
     <t>Sheep</t>
@@ -7467,7 +7473,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1188"/>
+  <dimension ref="A1:B1189"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -16887,12 +16893,12 @@
         <v>2346</v>
       </c>
       <c r="B1177" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="B1178" t="s">
         <v>2348</v>
@@ -16959,15 +16965,15 @@
         <v>2363</v>
       </c>
       <c r="B1186" t="s">
-        <v>2217</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="B1187" t="s">
-        <v>2365</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
@@ -16978,8 +16984,16 @@
         <v>2367</v>
       </c>
     </row>
+    <row r="1189" spans="1:2">
+      <c r="A1189" t="s">
+        <v>2368</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>2369</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1188"/>
+  <autoFilter ref="A1:B1189"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -1957,6 +1957,12 @@
     <t>おとぎ話</t>
   </si>
   <si>
+    <t>Fall Drop</t>
+  </si>
+  <si>
+    <t>フォール・ドロップ</t>
+  </si>
+  <si>
     <t>Fall Guys</t>
   </si>
   <si>
@@ -7121,12 +7127,6 @@
   </si>
   <si>
     <t>ハイピクセル（突然変異）タグ</t>
-  </si>
-  <si>
-    <t>Fall Drop</t>
-  </si>
-  <si>
-    <t>フォール・ドロップ</t>
   </si>
 </sst>
 </file>
@@ -10133,12 +10133,12 @@
         <v>660</v>
       </c>
       <c r="B332" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B333" t="s">
         <v>662</v>
@@ -11341,12 +11341,12 @@
         <v>961</v>
       </c>
       <c r="B483" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B484" t="s">
         <v>963</v>
@@ -14581,12 +14581,12 @@
         <v>1770</v>
       </c>
       <c r="B888" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B889" t="s">
         <v>1772</v>
@@ -14877,12 +14877,12 @@
         <v>1843</v>
       </c>
       <c r="B925" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B926" t="s">
         <v>1845</v>
@@ -16901,12 +16901,12 @@
         <v>2348</v>
       </c>
       <c r="B1178" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="B1179" t="s">
         <v>2350</v>
@@ -16973,15 +16973,15 @@
         <v>2365</v>
       </c>
       <c r="B1187" t="s">
-        <v>2219</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="B1188" t="s">
-        <v>2367</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="1189" spans="1:2">

--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2372">
   <si>
     <t>en</t>
   </si>
@@ -5273,6 +5273,12 @@
   </si>
   <si>
     <t>プレデター</t>
+  </si>
+  <si>
+    <t>Prehistoric Creature</t>
+  </si>
+  <si>
+    <t>先史時代の生物</t>
   </si>
   <si>
     <t>Present</t>
@@ -7473,7 +7479,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1189"/>
+  <dimension ref="A1:B1190"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14589,12 +14595,12 @@
         <v>1772</v>
       </c>
       <c r="B889" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B890" t="s">
         <v>1774</v>
@@ -14885,12 +14891,12 @@
         <v>1845</v>
       </c>
       <c r="B926" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B927" t="s">
         <v>1847</v>
@@ -16909,12 +16915,12 @@
         <v>2350</v>
       </c>
       <c r="B1179" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="B1180" t="s">
         <v>2352</v>
@@ -16981,19 +16987,27 @@
         <v>2367</v>
       </c>
       <c r="B1188" t="s">
-        <v>2221</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="B1189" t="s">
-        <v>2369</v>
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:2">
+      <c r="A1190" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>2371</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1189"/>
+  <autoFilter ref="A1:B1190"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2374">
   <si>
     <t>en</t>
   </si>
@@ -413,6 +413,12 @@
   </si>
   <si>
     <t>バック・トゥ・ザ・フューチャー</t>
+  </si>
+  <si>
+    <t>Backrooms (Movie)</t>
+  </si>
+  <si>
+    <t>『バックルームズ』（映画）</t>
   </si>
   <si>
     <t>Bag</t>
@@ -7479,7 +7485,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1190"/>
+  <dimension ref="A1:B1191"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -9339,12 +9345,12 @@
         <v>462</v>
       </c>
       <c r="B232" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B233" t="s">
         <v>464</v>
@@ -9619,15 +9625,15 @@
         <v>531</v>
       </c>
       <c r="B267" t="s">
-        <v>498</v>
+        <v>532</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B268" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -10147,12 +10153,12 @@
         <v>662</v>
       </c>
       <c r="B333" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B334" t="s">
         <v>664</v>
@@ -11355,12 +11361,12 @@
         <v>963</v>
       </c>
       <c r="B484" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B485" t="s">
         <v>965</v>
@@ -14603,12 +14609,12 @@
         <v>1774</v>
       </c>
       <c r="B890" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B891" t="s">
         <v>1776</v>
@@ -14899,12 +14905,12 @@
         <v>1847</v>
       </c>
       <c r="B927" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="B928" t="s">
         <v>1849</v>
@@ -16923,12 +16929,12 @@
         <v>2352</v>
       </c>
       <c r="B1180" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="B1181" t="s">
         <v>2354</v>
@@ -16995,19 +17001,27 @@
         <v>2369</v>
       </c>
       <c r="B1189" t="s">
-        <v>2223</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="B1190" t="s">
-        <v>2371</v>
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:2">
+      <c r="A1191" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>2373</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1190"/>
+  <autoFilter ref="A1:B1191"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2376">
   <si>
     <t>en</t>
   </si>
@@ -1544,6 +1544,12 @@
   </si>
   <si>
     <t>ディアブロ</t>
+  </si>
+  <si>
+    <t>Die of Death</t>
+  </si>
+  <si>
+    <t>死のダイス</t>
   </si>
   <si>
     <t>Digimon</t>
@@ -7485,7 +7491,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1191"/>
+  <dimension ref="A1:B1192"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -9633,15 +9639,15 @@
         <v>533</v>
       </c>
       <c r="B268" t="s">
-        <v>500</v>
+        <v>534</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B269" t="s">
-        <v>535</v>
+        <v>500</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -10161,12 +10167,12 @@
         <v>664</v>
       </c>
       <c r="B334" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B335" t="s">
         <v>666</v>
@@ -11369,12 +11375,12 @@
         <v>965</v>
       </c>
       <c r="B485" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B486" t="s">
         <v>967</v>
@@ -14617,12 +14623,12 @@
         <v>1776</v>
       </c>
       <c r="B891" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B892" t="s">
         <v>1778</v>
@@ -14913,12 +14919,12 @@
         <v>1849</v>
       </c>
       <c r="B928" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="B929" t="s">
         <v>1851</v>
@@ -16937,12 +16943,12 @@
         <v>2354</v>
       </c>
       <c r="B1181" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="B1182" t="s">
         <v>2356</v>
@@ -17009,19 +17015,27 @@
         <v>2371</v>
       </c>
       <c r="B1190" t="s">
-        <v>2225</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="B1191" t="s">
-        <v>2373</v>
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:2">
+      <c r="A1192" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>2375</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1191"/>
+  <autoFilter ref="A1:B1192"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/ja/headTags.xlsx
+++ b/lang/ja/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1193</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2378">
   <si>
     <t>en</t>
   </si>
@@ -2492,6 +2492,12 @@
   </si>
   <si>
     <t>フォント（オレンジ）</t>
+  </si>
+  <si>
+    <t>Font (Pale Oak)</t>
+  </si>
+  <si>
+    <t>フォント（ペール・オーク）</t>
   </si>
   <si>
     <t>Font (Pink)</t>
@@ -7491,7 +7497,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1192"/>
+  <dimension ref="A1:B1193"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -11383,12 +11389,12 @@
         <v>967</v>
       </c>
       <c r="B486" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B487" t="s">
         <v>969</v>
@@ -14631,12 +14637,12 @@
         <v>1778</v>
       </c>
       <c r="B892" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B893" t="s">
         <v>1780</v>
@@ -14927,12 +14933,12 @@
         <v>1851</v>
       </c>
       <c r="B929" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B930" t="s">
         <v>1853</v>
@@ -16951,12 +16957,12 @@
         <v>2356</v>
       </c>
       <c r="B1182" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="B1183" t="s">
         <v>2358</v>
@@ -17023,19 +17029,27 @@
         <v>2373</v>
       </c>
       <c r="B1191" t="s">
-        <v>2227</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="B1192" t="s">
-        <v>2375</v>
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:2">
+      <c r="A1193" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>2377</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1192"/>
+  <autoFilter ref="A1:B1193"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
